--- a/templates/CAPITANIA PREV BP - template.xlsx
+++ b/templates/CAPITANIA PREV BP - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1282,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="57" min="1" max="1"/>
@@ -1290,8 +1290,8 @@
     <col width="5.42578125" customWidth="1" style="57" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="57" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="57" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="57" min="10" max="18"/>
-    <col width="9.140625" customWidth="1" style="57" min="19" max="16384"/>
+    <col width="9.140625" customWidth="1" style="57" min="10" max="19"/>
+    <col width="9.140625" customWidth="1" style="57" min="20" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1434,96 +1434,96 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="34" t="n">
-        <v>1.5845744</v>
+        <v>1.6045773</v>
       </c>
       <c r="D17" s="35" t="n">
-        <v>-0.000221903090623532</v>
+        <v>0.002480809618104152</v>
       </c>
       <c r="E17" s="35" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>-0.4089155744664764</v>
+        <v>4.571552776838348</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="38" t="n">
-        <v>1.5849261</v>
+        <v>1.6006065</v>
       </c>
       <c r="D18" s="39" t="n">
-        <v>-0.007072044072269468</v>
+        <v>-0.0001787752545813204</v>
       </c>
       <c r="E18" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>-13.03212567404249</v>
+        <v>-0.3294410443860614</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="38" t="n">
-        <v>1.5962146</v>
+        <v>1.6008927</v>
       </c>
       <c r="D19" s="39" t="n">
-        <v>-0.001234273431798272</v>
+        <v>0.001776661419658376</v>
       </c>
       <c r="E19" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>-2.27447769201542</v>
+        <v>3.273972088494145</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="38" t="n">
-        <v>1.5981872</v>
+        <v>1.5980535</v>
       </c>
       <c r="D20" s="39" t="n">
-        <v>0.0005223016153788063</v>
+        <v>-0.002088799258897711</v>
       </c>
       <c r="E20" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>0.9624799028136841</v>
+        <v>-3.849169231925647</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B21" s="37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="38" t="n">
-        <v>1.5973529</v>
+        <v>1.6013985</v>
       </c>
       <c r="D21" s="39" t="n">
-        <v>0.0001805186840908579</v>
+        <v>0.001613566316180703</v>
       </c>
       <c r="E21" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>0.3326537778249293</v>
+        <v>2.973425900769396</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1563,18 +1563,18 @@
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="41" t="inlineStr"/>
       <c r="D24" s="35" t="n">
-        <v>-0.009564798391676232</v>
+        <v>0.009189439474947436</v>
       </c>
       <c r="E24" s="35" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="36" t="n">
-        <v>-0.9123784340267757</v>
+        <v>2.415206077720178</v>
       </c>
       <c r="G24" s="42" t="n"/>
     </row>
@@ -1587,13 +1587,13 @@
       </c>
       <c r="C25" s="44" t="inlineStr"/>
       <c r="D25" s="39" t="n">
-        <v>-0.005361068678523706</v>
+        <v>0.00220493200980787</v>
       </c>
       <c r="E25" s="39" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>-0.462246566246225</v>
+        <v>0.1915596346184205</v>
       </c>
       <c r="G25" s="45" t="n"/>
     </row>
@@ -1606,13 +1606,13 @@
       </c>
       <c r="C26" s="44" t="inlineStr"/>
       <c r="D26" s="39" t="n">
-        <v>0.0153850038040706</v>
+        <v>0.0220515551601308</v>
       </c>
       <c r="E26" s="39" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="40" t="n">
-        <v>0.4359823096069129</v>
+        <v>0.6264885566934955</v>
       </c>
       <c r="G26" s="45" t="n"/>
     </row>
@@ -1625,13 +1625,13 @@
       </c>
       <c r="C27" s="44" t="inlineStr"/>
       <c r="D27" s="39" t="n">
-        <v>0.05185777107830303</v>
+        <v>0.0619633190589044</v>
       </c>
       <c r="E27" s="39" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F27" s="40" t="n">
-        <v>0.7215711950004443</v>
+        <v>0.8632969691216681</v>
       </c>
       <c r="G27" s="45" t="n"/>
     </row>
@@ -1644,13 +1644,13 @@
       </c>
       <c r="C28" s="44" t="inlineStr"/>
       <c r="D28" s="39" t="n">
-        <v>0.1309970721791354</v>
+        <v>0.1428063821717973</v>
       </c>
       <c r="E28" s="39" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F28" s="40" t="n">
-        <v>0.886211476514063</v>
+        <v>0.964803448177309</v>
       </c>
       <c r="G28" s="45" t="n"/>
     </row>
@@ -1658,18 +1658,18 @@
       <c r="A29" s="46" t="n"/>
       <c r="B29" s="44" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="44" t="inlineStr"/>
       <c r="D29" s="39" t="n">
-        <v>0.01020311428861209</v>
+        <v>0.2434714500464741</v>
       </c>
       <c r="E29" s="39" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F29" s="40" t="n">
-        <v>0.3145320896965479</v>
+        <v>0.8760156845689937</v>
       </c>
       <c r="G29" s="45" t="n"/>
     </row>
@@ -1677,18 +1677,18 @@
       <c r="A30" s="46" t="n"/>
       <c r="B30" s="44" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="44" t="inlineStr"/>
       <c r="D30" s="39" t="n">
-        <v>0.1592531240420054</v>
+        <v>0.0229554292791887</v>
       </c>
       <c r="E30" s="39" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F30" s="40" t="n">
-        <v>1.112625326885719</v>
+        <v>0.6032110755809541</v>
       </c>
       <c r="G30" s="45" t="n"/>
     </row>
@@ -1696,18 +1696,18 @@
       <c r="A31" s="46" t="n"/>
       <c r="B31" s="44" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr"/>
       <c r="D31" s="39" t="n">
-        <v>0.0833304710583973</v>
+        <v>0.1592531240420054</v>
       </c>
       <c r="E31" s="39" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F31" s="40" t="n">
-        <v>0.7630651269878536</v>
+        <v>1.112625326885719</v>
       </c>
       <c r="G31" s="45" t="n"/>
     </row>
@@ -1715,161 +1715,180 @@
       <c r="A32" s="46" t="n"/>
       <c r="B32" s="44" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="44" t="inlineStr"/>
       <c r="D32" s="39" t="n">
-        <v>0.5845743999999999</v>
+        <v>0.0833304710583973</v>
       </c>
       <c r="E32" s="39" t="n">
-        <v>0.6526451236503434</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F32" s="40" t="n">
-        <v>0.8957002493642892</v>
+        <v>0.7630651269878536</v>
       </c>
       <c r="G32" s="45" t="n"/>
     </row>
-    <row r="33" ht="15.95" customHeight="1">
-      <c r="A33" s="12" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
+    <row r="33" ht="15.95" customFormat="1" customHeight="1" s="32">
+      <c r="A33" s="46" t="n"/>
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="inlineStr"/>
+      <c r="D33" s="39" t="n">
+        <v>0.6045773000000001</v>
+      </c>
+      <c r="E33" s="39" t="n">
+        <v>0.66163533877394</v>
+      </c>
+      <c r="F33" s="40" t="n">
+        <v>0.9137621051504402</v>
+      </c>
+      <c r="G33" s="45" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customHeight="1">
       <c r="A34" s="12" t="n"/>
-      <c r="B34" s="56" t="inlineStr">
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="A35" s="12" t="n"/>
+      <c r="B35" s="56" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="A35" s="15" t="n"/>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="47" t="n">
-        <v>108406009.1016</v>
-      </c>
-      <c r="F35" s="29" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="15" t="n"/>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C36" s="14" t="n"/>
       <c r="D36" s="14" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>109423176.3913798</v>
+        <v>109558306.5911</v>
       </c>
       <c r="F36" s="29" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="15" t="n"/>
-      <c r="B37" s="17" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="47" t="n">
+        <v>109124627.3467932</v>
+      </c>
+      <c r="F37" s="29" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="21" t="n"/>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="20" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="19" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C39" s="31" t="inlineStr">
+      <c r="C40" s="31" t="inlineStr">
         <is>
           <t>2022-01-26</t>
         </is>
       </c>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="23" t="n"/>
-      <c r="C40" s="24" t="n"/>
       <c r="D40" s="22" t="n"/>
       <c r="E40" s="22" t="n"/>
       <c r="F40" s="22" t="n"/>
       <c r="G40" s="4" t="n"/>
     </row>
-    <row r="41" ht="54" customHeight="1">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="58" t="inlineStr">
+    <row r="41" ht="15.95" customHeight="1">
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="24" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="54" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="58" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="59" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="25" t="n"/>
-      <c r="C43" s="25" t="n"/>
-      <c r="D43" s="25" t="n"/>
-      <c r="E43" s="25" t="n"/>
-      <c r="F43" s="25" t="n"/>
+      <c r="B43" s="59" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="26" t="n"/>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
+      <c r="B44" s="25" t="n"/>
+      <c r="C44" s="25" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="25" t="n"/>
+      <c r="F44" s="25" t="n"/>
       <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="26" t="n"/>
       <c r="C45" s="27" t="n"/>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="26" t="n"/>
+      <c r="C46" s="27" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="86" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="83"/>
 </worksheet>
 </file>